--- a/HARGA ONLINE.xlsx
+++ b/HARGA ONLINE.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCEE9239-74A8-4F2A-A8B4-56FFE9A1826D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04B19C03-9154-49BF-865A-9177352C7182}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3930" yWindow="2835" windowWidth="15360" windowHeight="8085" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -893,7 +893,7 @@
         <v>8</v>
       </c>
       <c r="E6" s="5">
-        <v>14500</v>
+        <v>14900</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
@@ -911,7 +911,7 @@
         <v>8</v>
       </c>
       <c r="E7" s="5">
-        <v>14500</v>
+        <v>14900</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
@@ -2280,7 +2280,7 @@
         <v>24</v>
       </c>
       <c r="E89" s="10">
-        <v>14500</v>
+        <v>14900</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.25">
@@ -2288,7 +2288,7 @@
         <v>67</v>
       </c>
       <c r="E90" s="10">
-        <v>14500</v>
+        <v>14900</v>
       </c>
     </row>
     <row r="91" spans="1:5" s="15" customFormat="1" x14ac:dyDescent="0.25">
@@ -2543,7 +2543,7 @@
         <v>81</v>
       </c>
       <c r="E107" s="16">
-        <v>14500</v>
+        <v>14900</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.25">
@@ -2618,7 +2618,7 @@
         <v>69</v>
       </c>
       <c r="E112" s="13">
-        <v>14500</v>
+        <v>14900</v>
       </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.25">
@@ -2633,7 +2633,7 @@
         <v>69</v>
       </c>
       <c r="E113" s="13">
-        <v>14500</v>
+        <v>14900</v>
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.25">

--- a/HARGA ONLINE.xlsx
+++ b/HARGA ONLINE.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04B19C03-9154-49BF-865A-9177352C7182}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29F30D71-E2EC-4A22-93D4-C527805F51D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3930" yWindow="2835" windowWidth="15360" windowHeight="8085" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="372" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="376" uniqueCount="116">
   <si>
     <t>No.</t>
   </si>
@@ -361,6 +361,18 @@
   </si>
   <si>
     <t>A3</t>
+  </si>
+  <si>
+    <t>Komik Pahlawan, Pendidikan Sejarah Untuk Anak | Jakarta</t>
+  </si>
+  <si>
+    <t>Komik Pahlawan, Pendidikan Sejarah Untuk Anak</t>
+  </si>
+  <si>
+    <t>Komik Pahlawan</t>
+  </si>
+  <si>
+    <t>Pendidikan Sejarah Untuk Anak</t>
   </si>
 </sst>
 </file>
@@ -463,7 +475,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -512,6 +524,12 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -793,7 +811,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E125"/>
+  <dimension ref="A1:E129"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="42.140625" bestFit="1" customWidth="1"/>
@@ -916,7 +934,7 @@
     </row>
     <row r="8" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
-        <f t="shared" ref="A8:A76" si="0">A7+1</f>
+        <f t="shared" ref="A8:A75" si="0">A7+1</f>
         <v>3</v>
       </c>
       <c r="B8" s="4" t="s">
@@ -2082,468 +2100,452 @@
       </c>
     </row>
     <row r="76" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A76" s="3">
-        <f t="shared" si="0"/>
+      <c r="A76" s="3"/>
+      <c r="B76" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="C76" s="20"/>
+      <c r="D76" s="11"/>
+      <c r="E76" s="21">
+        <v>10800</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A77" s="3"/>
+      <c r="B77" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="C77" s="20"/>
+      <c r="D77" s="11"/>
+      <c r="E77" s="21">
+        <v>10800</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A78" s="3"/>
+      <c r="B78" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="C78" s="20"/>
+      <c r="D78" s="11"/>
+      <c r="E78" s="21">
+        <v>10800</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A79" s="3"/>
+      <c r="B79" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="C79" s="20"/>
+      <c r="D79" s="11"/>
+      <c r="E79" s="21">
+        <v>10800</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A80" s="3">
+        <f>A75+1</f>
         <v>39</v>
       </c>
-      <c r="B76" s="9" t="s">
+      <c r="B80" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="C76" s="11" t="s">
+      <c r="C80" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="D76" s="11" t="s">
+      <c r="D80" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="E76" s="10">
+      <c r="E80" s="10">
         <v>4750</v>
       </c>
     </row>
-    <row r="77" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A77" s="12"/>
-      <c r="B77" s="9" t="s">
+    <row r="81" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A81" s="12"/>
+      <c r="B81" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="C77" s="12" t="s">
+      <c r="C81" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="D77" s="3" t="s">
+      <c r="D81" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="E77" s="10">
+      <c r="E81" s="10">
         <v>725000</v>
       </c>
     </row>
-    <row r="78" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A78" s="12"/>
-      <c r="B78" s="9" t="s">
+    <row r="82" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A82" s="12"/>
+      <c r="B82" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="C78" s="12" t="s">
+      <c r="C82" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="D78" s="3" t="s">
+      <c r="D82" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E78" s="10">
+      <c r="E82" s="10">
         <v>625000</v>
       </c>
     </row>
-    <row r="79" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B79" s="9" t="s">
+    <row r="83" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B83" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="C79" s="12" t="s">
+      <c r="C83" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="D79" s="3" t="s">
+      <c r="D83" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="E79" s="10">
+      <c r="E83" s="10">
         <v>400000</v>
       </c>
     </row>
-    <row r="80" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B80" s="18" t="s">
+    <row r="84" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B84" s="18" t="s">
         <v>104</v>
       </c>
-      <c r="C80" s="12" t="s">
+      <c r="C84" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="D80" s="3" t="s">
+      <c r="D84" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="E80" s="10">
+      <c r="E84" s="10">
         <v>725000</v>
       </c>
     </row>
-    <row r="81" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B81" s="18" t="s">
+    <row r="85" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B85" s="18" t="s">
         <v>104</v>
       </c>
-      <c r="C81" s="12" t="s">
+      <c r="C85" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="D81" s="3" t="s">
+      <c r="D85" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E81" s="10">
+      <c r="E85" s="10">
         <v>625000</v>
       </c>
     </row>
-    <row r="82" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B82" s="18" t="s">
+    <row r="86" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B86" s="18" t="s">
         <v>104</v>
       </c>
-      <c r="C82" s="12" t="s">
+      <c r="C86" s="12" t="s">
         <v>64</v>
-      </c>
-      <c r="D82" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E82" s="10">
-        <v>400000</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B83" t="s">
-        <v>62</v>
-      </c>
-      <c r="C83" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="D83" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="E83" s="10">
-        <v>725000</v>
-      </c>
-    </row>
-    <row r="84" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B84" t="s">
-        <v>62</v>
-      </c>
-      <c r="C84" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="D84" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E84" s="10">
-        <v>625000</v>
-      </c>
-    </row>
-    <row r="85" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B85" t="s">
-        <v>62</v>
-      </c>
-      <c r="C85" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="D85" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E85" s="10">
-        <v>400000</v>
-      </c>
-    </row>
-    <row r="86" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B86" t="s">
-        <v>65</v>
-      </c>
-      <c r="C86" s="12" t="s">
-        <v>66</v>
       </c>
       <c r="D86" s="3" t="s">
         <v>14</v>
       </c>
       <c r="E86" s="10">
-        <v>8500</v>
+        <v>400000</v>
       </c>
     </row>
     <row r="87" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B87" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C87" s="12" t="s">
-        <v>66</v>
+        <v>6</v>
       </c>
       <c r="D87" s="3" t="s">
         <v>24</v>
       </c>
       <c r="E87" s="10">
-        <v>21000</v>
+        <v>725000</v>
       </c>
     </row>
     <row r="88" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B88" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C88" s="12" t="s">
-        <v>10</v>
+        <v>63</v>
       </c>
       <c r="D88" s="3" t="s">
         <v>13</v>
       </c>
       <c r="E88" s="10">
-        <v>12500</v>
+        <v>625000</v>
       </c>
     </row>
     <row r="89" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B89" t="s">
+        <v>62</v>
+      </c>
+      <c r="C89" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="D89" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E89" s="10">
+        <v>400000</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B90" t="s">
         <v>65</v>
       </c>
-      <c r="C89" s="12" t="s">
+      <c r="C90" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="D90" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E90" s="10">
+        <v>8500</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B91" t="s">
+        <v>65</v>
+      </c>
+      <c r="C91" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="D91" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E91" s="10">
+        <v>21000</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B92" t="s">
+        <v>65</v>
+      </c>
+      <c r="C92" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="D92" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E92" s="10">
+        <v>12500</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B93" t="s">
+        <v>65</v>
+      </c>
+      <c r="C93" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="D89" s="3" t="s">
+      <c r="D93" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="E89" s="10">
+      <c r="E93" s="10">
         <v>14900</v>
       </c>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B90" t="s">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B94" t="s">
         <v>67</v>
       </c>
-      <c r="E90" s="10">
+      <c r="E94" s="10">
         <v>14900</v>
       </c>
     </row>
-    <row r="91" spans="1:5" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="14"/>
-      <c r="B91" t="s">
+    <row r="95" spans="1:5" s="15" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A95" s="14"/>
+      <c r="B95" t="s">
         <v>83</v>
       </c>
-      <c r="C91" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="D91" s="14" t="s">
+      <c r="C95" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="D95" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="E91" s="14">
+      <c r="E95" s="14">
         <v>12500</v>
-      </c>
-    </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A92" s="13"/>
-      <c r="B92" t="s">
-        <v>83</v>
-      </c>
-      <c r="C92" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="D92" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="E92" s="13">
-        <v>28000</v>
-      </c>
-    </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A93" s="13"/>
-      <c r="B93" t="s">
-        <v>84</v>
-      </c>
-      <c r="C93" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="D93" s="13" t="s">
-        <v>68</v>
-      </c>
-      <c r="E93" s="13">
-        <v>14000</v>
-      </c>
-    </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A94" s="13"/>
-      <c r="B94" t="s">
-        <v>85</v>
-      </c>
-      <c r="C94" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="D94" s="13" t="s">
-        <v>69</v>
-      </c>
-      <c r="E94" s="13">
-        <v>75000</v>
-      </c>
-    </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A95" s="13"/>
-      <c r="B95" t="s">
-        <v>86</v>
-      </c>
-      <c r="C95" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="D95" s="13" t="s">
-        <v>69</v>
-      </c>
-      <c r="E95" s="13">
-        <v>72000</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A96" s="13"/>
       <c r="B96" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="C96" s="13" t="s">
         <v>10</v>
       </c>
       <c r="D96" s="13" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E96" s="13">
-        <v>50000</v>
+        <v>28000</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" s="13"/>
       <c r="B97" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C97" s="13" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D97" s="13" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E97" s="13">
-        <v>26000</v>
+        <v>14000</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98" s="13"/>
       <c r="B98" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="C98" s="13" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D98" s="13" t="s">
         <v>69</v>
       </c>
       <c r="E98" s="13">
-        <v>21000</v>
+        <v>75000</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99" s="13"/>
       <c r="B99" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C99" s="13" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D99" s="13" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E99" s="13">
-        <v>18500</v>
+        <v>72000</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A100" s="13"/>
       <c r="B100" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C100" s="13" t="s">
         <v>10</v>
       </c>
       <c r="D100" s="13" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="E100" s="13">
-        <v>24000</v>
+        <v>50000</v>
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A101" s="13"/>
       <c r="B101" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C101" s="13" t="s">
         <v>10</v>
       </c>
       <c r="D101" s="13" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="E101" s="13">
-        <v>39000</v>
+        <v>26000</v>
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A102" s="13"/>
       <c r="B102" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C102" s="13" t="s">
-        <v>70</v>
+        <v>10</v>
       </c>
       <c r="D102" s="13" t="s">
         <v>69</v>
       </c>
       <c r="E102" s="13">
-        <v>9000</v>
+        <v>21000</v>
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A103" s="13"/>
       <c r="B103" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C103" s="13" t="s">
         <v>10</v>
       </c>
       <c r="D103" s="13" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E103" s="13">
-        <v>7200</v>
+        <v>18500</v>
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A104" s="13"/>
       <c r="B104" t="s">
-        <v>92</v>
-      </c>
-      <c r="C104" t="s">
-        <v>16</v>
-      </c>
-      <c r="D104" t="s">
-        <v>80</v>
-      </c>
-      <c r="E104" s="16">
-        <v>26000</v>
+        <v>89</v>
+      </c>
+      <c r="C104" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="D104" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="E104" s="13">
+        <v>24000</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A105" s="13"/>
       <c r="B105" t="s">
-        <v>92</v>
-      </c>
-      <c r="C105" t="s">
-        <v>20</v>
-      </c>
-      <c r="D105" t="s">
-        <v>80</v>
-      </c>
-      <c r="E105" s="16">
-        <v>24000</v>
+        <v>89</v>
+      </c>
+      <c r="C105" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="D105" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="E105" s="13">
+        <v>39000</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A106" s="13"/>
       <c r="B106" t="s">
-        <v>92</v>
-      </c>
-      <c r="C106" t="s">
-        <v>79</v>
-      </c>
-      <c r="D106" t="s">
-        <v>80</v>
-      </c>
-      <c r="E106" s="16">
-        <v>18000</v>
+        <v>90</v>
+      </c>
+      <c r="C106" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="D106" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="E106" s="13">
+        <v>9000</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A107" s="13"/>
       <c r="B107" t="s">
-        <v>92</v>
-      </c>
-      <c r="C107" t="s">
-        <v>79</v>
-      </c>
-      <c r="D107" t="s">
-        <v>81</v>
-      </c>
-      <c r="E107" s="16">
-        <v>14900</v>
+        <v>91</v>
+      </c>
+      <c r="C107" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="D107" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="E107" s="13">
+        <v>7200</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.25">
@@ -2552,100 +2554,100 @@
         <v>92</v>
       </c>
       <c r="C108" t="s">
-        <v>79</v>
+        <v>16</v>
       </c>
       <c r="D108" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E108" s="16">
-        <v>12500</v>
+        <v>26000</v>
       </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A109" s="13"/>
       <c r="B109" t="s">
-        <v>93</v>
-      </c>
-      <c r="C109" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="D109" s="13" t="s">
-        <v>68</v>
-      </c>
-      <c r="E109" s="13">
-        <v>14500</v>
+        <v>92</v>
+      </c>
+      <c r="C109" t="s">
+        <v>20</v>
+      </c>
+      <c r="D109" t="s">
+        <v>80</v>
+      </c>
+      <c r="E109" s="16">
+        <v>24000</v>
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A110" s="13"/>
       <c r="B110" t="s">
-        <v>94</v>
-      </c>
-      <c r="C110" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="D110" s="13" t="s">
-        <v>69</v>
-      </c>
-      <c r="E110" s="13">
+        <v>92</v>
+      </c>
+      <c r="C110" t="s">
+        <v>79</v>
+      </c>
+      <c r="D110" t="s">
+        <v>80</v>
+      </c>
+      <c r="E110" s="16">
         <v>18000</v>
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A111" s="13"/>
       <c r="B111" t="s">
-        <v>94</v>
-      </c>
-      <c r="C111" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="D111" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="E111" s="13">
-        <v>27000</v>
+        <v>92</v>
+      </c>
+      <c r="C111" t="s">
+        <v>79</v>
+      </c>
+      <c r="D111" t="s">
+        <v>81</v>
+      </c>
+      <c r="E111" s="16">
+        <v>14900</v>
       </c>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A112" s="13"/>
       <c r="B112" t="s">
-        <v>95</v>
-      </c>
-      <c r="C112" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="D112" s="13" t="s">
-        <v>69</v>
-      </c>
-      <c r="E112" s="13">
-        <v>14900</v>
+        <v>92</v>
+      </c>
+      <c r="C112" t="s">
+        <v>79</v>
+      </c>
+      <c r="D112" t="s">
+        <v>82</v>
+      </c>
+      <c r="E112" s="16">
+        <v>12500</v>
       </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A113" s="13"/>
       <c r="B113" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="C113" s="13" t="s">
-        <v>70</v>
+        <v>10</v>
       </c>
       <c r="D113" s="13" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E113" s="13">
-        <v>14900</v>
+        <v>14500</v>
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A114" s="13"/>
       <c r="B114" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C114" s="13" t="s">
-        <v>72</v>
+        <v>10</v>
       </c>
       <c r="D114" s="13" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E114" s="13">
         <v>18000</v>
@@ -2654,153 +2656,213 @@
     <row r="115" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A115" s="13"/>
       <c r="B115" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="C115" s="13" t="s">
-        <v>73</v>
+        <v>10</v>
       </c>
       <c r="D115" s="13" t="s">
-        <v>37</v>
+        <v>77</v>
       </c>
       <c r="E115" s="13">
-        <v>14325</v>
+        <v>27000</v>
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A116" s="13"/>
       <c r="B116" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="C116" s="13" t="s">
-        <v>37</v>
+        <v>70</v>
       </c>
       <c r="D116" s="13" t="s">
-        <v>37</v>
+        <v>69</v>
       </c>
       <c r="E116" s="13">
-        <v>8100</v>
+        <v>14900</v>
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A117" s="13"/>
       <c r="B117" t="s">
-        <v>100</v>
-      </c>
-      <c r="C117" s="13"/>
+        <v>96</v>
+      </c>
+      <c r="C117" s="13" t="s">
+        <v>70</v>
+      </c>
       <c r="D117" s="13" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E117" s="13">
-        <v>8500</v>
+        <v>14900</v>
       </c>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A118" s="13"/>
       <c r="B118" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="C118" s="13" t="s">
-        <v>37</v>
+        <v>72</v>
       </c>
       <c r="D118" s="13" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E118" s="13">
-        <v>12500</v>
+        <v>18000</v>
       </c>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A119" s="13"/>
       <c r="B119" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C119" s="13" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D119" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="E119" s="17">
-        <v>25577</v>
+      <c r="E119" s="13">
+        <v>14325</v>
       </c>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A120" s="13"/>
       <c r="B120" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C120" s="13" t="s">
-        <v>75</v>
+        <v>37</v>
       </c>
       <c r="D120" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="E120" s="17">
-        <v>25577</v>
+      <c r="E120" s="13">
+        <v>8100</v>
       </c>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A121" s="13"/>
       <c r="B121" t="s">
+        <v>100</v>
+      </c>
+      <c r="C121" s="13"/>
+      <c r="D121" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="E121" s="13">
+        <v>8500</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A122" s="13"/>
+      <c r="B122" t="s">
+        <v>100</v>
+      </c>
+      <c r="C122" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="D122" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="E122" s="13">
+        <v>12500</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A123" s="13"/>
+      <c r="B123" t="s">
+        <v>101</v>
+      </c>
+      <c r="C123" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="D123" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="E123" s="17">
+        <v>25577</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A124" s="13"/>
+      <c r="B124" t="s">
+        <v>102</v>
+      </c>
+      <c r="C124" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="D124" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="E124" s="17">
+        <v>25577</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A125" s="13"/>
+      <c r="B125" t="s">
         <v>103</v>
       </c>
-      <c r="C121" s="13" t="s">
+      <c r="C125" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="D121" s="13" t="s">
+      <c r="D125" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="E121" s="17">
+      <c r="E125" s="17">
         <v>25577</v>
       </c>
     </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B122" t="s">
+    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B126" t="s">
         <v>105</v>
       </c>
-      <c r="C122" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="D122" s="13" t="s">
+      <c r="C126" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="D126" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="E122" s="13">
+      <c r="E126" s="13">
         <v>14500</v>
       </c>
     </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B123" t="s">
+    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B127" t="s">
         <v>106</v>
       </c>
-      <c r="D123" s="13" t="s">
+      <c r="D127" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="E123" s="19">
+      <c r="E127" s="19">
         <v>14500</v>
       </c>
     </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B124" t="s">
+    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B128" t="s">
         <v>107</v>
       </c>
-      <c r="D124" s="13" t="s">
+      <c r="D128" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="E124" s="19">
+      <c r="E128" s="19">
         <v>14500</v>
       </c>
     </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B125" t="s">
+    <row r="129" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B129" t="s">
         <v>108</v>
       </c>
-      <c r="C125" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="D125" s="13" t="s">
+      <c r="C129" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="D129" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="E125" s="19">
+      <c r="E129" s="19">
         <v>14500</v>
       </c>
     </row>
